--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי אשרת – ירח סגול</v>
+        <v>יונתן רזאל – היינו כחולמים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a7%d7%95%d7%91%d7%99-%d7%90%d7%a9%d7%a8%d7%aa-%d7%99%d7%a8%d7%97-%d7%a1%d7%92%d7%95%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%aa%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%94%d7%99%d7%99%d7%a0%d7%95-%d7%9b%d7%97%d7%95%d7%9c%d7%9e%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-08</v>
+        <v>2026-04-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"ירח סגול” שהלחין ושר קובי אשרת (מילים: שמרית אור) נכתב לפני כ-15 שנה, עוסק במזרח התיכון. זה שיר שאינו צועק, אבל נוגע בכל מה שעבר ועובר על ישראל. השיר בנוי כמו מהדורת חדשות: “יש ידיעות במזרח התיכון על אי־שקט גדול…”</v>
+        <v>יונתן רזאל לקח טקסט מקראי מוכר  מתוך ספר תהילים (שיר המעלות, תהילים קכ״ו) – והטעין אותו במשמעות אופטימית, במיוחד על רקע תקופה טעונה כמו מלחמה. הטקסט המקורי מתאר חזרה מציון (גאולה), זיכרון של בכי, הבטחה לשמחה עתידית. למעשה הוא מורכב</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי אשרת – ירח סגול</v>
+        <v>יונתן רזאל – היינו כחולמים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יונתן רזאל – היינו כחולמים</v>
+        <v>ערן צור – אדבר איתך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%aa%d7%9f-%d7%a8%d7%96%d7%90%d7%9c-%d7%94%d7%99%d7%99%d7%a0%d7%95-%d7%9b%d7%97%d7%95%d7%9c%d7%9e%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a2%d7%a8%d7%9f-%d7%a6%d7%95%d7%a8-%d7%90%d7%93%d7%91%d7%a8-%d7%90%d7%99%d7%aa%d7%9a/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יונתן רזאל לקח טקסט מקראי מוכר  מתוך ספר תהילים (שיר המעלות, תהילים קכ״ו) – והטעין אותו במשמעות אופטימית, במיוחד על רקע תקופה טעונה כמו מלחמה. הטקסט המקורי מתאר חזרה מציון (גאולה), זיכרון של בכי, הבטחה לשמחה עתידית. למעשה הוא מורכב</v>
+        <v>הקאבר של "אדבר איתך" בביצוע ערן צור לשיר המזוהה עם חוה אלברשטיין (מילים: רחל שפירא) הוא דוגמה נדירה לפרשנות שמצליחה לא רק לבצע שיר מחדש – אלא לשנות את נקודת המבט הרגשית שלו. במקור, מדובר בקול נשי שמדבר אל גבר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יונתן רזאל – היינו כחולמים</v>
+        <v>ערן צור – אדבר איתך</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ערן צור – אדבר איתך</v>
+        <v>שימי תבורי – עד מתי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a2%d7%a8%d7%9f-%d7%a6%d7%95%d7%a8-%d7%90%d7%93%d7%91%d7%a8-%d7%90%d7%99%d7%aa%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%a9%d7%99%d7%9e%d7%99-%d7%aa%d7%91%d7%95%d7%a8%d7%99-%d7%a2%d7%93-%d7%9e%d7%aa%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-09</v>
+        <v>2026-04-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הקאבר של "אדבר איתך" בביצוע ערן צור לשיר המזוהה עם חוה אלברשטיין (מילים: רחל שפירא) הוא דוגמה נדירה לפרשנות שמצליחה לא רק לבצע שיר מחדש – אלא לשנות את נקודת המבט הרגשית שלו. במקור, מדובר בקול נשי שמדבר אל גבר</v>
+        <v>שימי תבורי שר משאלה הכי בסיסית  עם ניסיון לנסח זעקה פשוטה וישירה נגד מציאות של מלחמות מתמשכות במוסיקה שמחברת פופ ים־תיכוני עם אסתטיקה של רוק אולד-סקול. מבחינתו אין חדש תחת השמש הים תיכונית אותה הגשה דרמטית בטון כמעט מקונן.  בשיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ערן צור – אדבר איתך</v>
+        <v>שימי תבורי – עד מתי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שימי תבורי – עד מתי</v>
+        <v>נועה קירל – בוחרת אותנו</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%99%d7%9e%d7%99-%d7%aa%d7%91%d7%95%d7%a8%d7%99-%d7%a2%d7%93-%d7%9e%d7%aa%d7%99/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%91%d7%95%d7%97%d7%a8%d7%aa-%d7%90%d7%95%d7%aa%d7%a0%d7%95/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>שימי תבורי שר משאלה הכי בסיסית  עם ניסיון לנסח זעקה פשוטה וישירה נגד מציאות של מלחמות מתמשכות במוסיקה שמחברת פופ ים־תיכוני עם אסתטיקה של רוק אולד-סקול. מבחינתו אין חדש תחת השמש הים תיכונית אותה הגשה דרמטית בטון כמעט מקונן.  בשיר</v>
+        <v>ב"בוחרת אותנו" נועה קירל מציגה ניסיון לשלב בין פופ עכשווי מלוטש לבין וידוי אישי על זוגיות תחת לחץ של חיים מודרניים אינטנסיביים. זהו שיר שמכוון להיות גם המנון רומנטי וגם הצצה לחיים “מאחורי הקלעים” של כוכבת. השיר בנוי באופן הדרגתי:</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שימי תבורי – עד מתי</v>
+        <v>נועה קירל – בוחרת אותנו</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה קירל – בוחרת אותנו</v>
+        <v>הסטרוקס Going Shopping</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a7%d7%99%d7%a8%d7%9c-%d7%91%d7%95%d7%97%d7%a8%d7%aa-%d7%90%d7%95%d7%aa%d7%a0%d7%95/</v>
+        <v>https://yosmusic.com/%d7%94%d7%a1%d7%98%d7%a8%d7%95%d7%a7%d7%a1-going-shopping/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-10</v>
+        <v>2026-04-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>ב"בוחרת אותנו" נועה קירל מציגה ניסיון לשלב בין פופ עכשווי מלוטש לבין וידוי אישי על זוגיות תחת לחץ של חיים מודרניים אינטנסיביים. זהו שיר שמכוון להיות גם המנון רומנטי וגם הצצה לחיים “מאחורי הקלעים” של כוכבת. השיר בנוי באופן הדרגתי:</v>
+        <v>הסטרוקס, גיבורי האינדי מניו יורק מוציאים את את הסינגל החדש שלהם “Going Shopping” לקראתהאלבום “Reality Awaits” שצפוי לצאת בקיץ הקרוב  זה החומר החדש הראשון שלהם מאז האלבום המוערך מ־2020, “The New Abnormal”, שיר קליל וזורם שמשלב בין גיטרות לסינתיסייזרים, ומאמץ</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה קירל – בוחרת אותנו</v>
+        <v>הסטרוקס Going Shopping</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>הסטרוקס Going Shopping</v>
+        <v>התקווה 6 – חופשת מלחמה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%a1%d7%98%d7%a8%d7%95%d7%a7%d7%a1-going-shopping/</v>
+        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%97%d7%95%d7%a4%d7%a9%d7%aa-%d7%9e%d7%9c%d7%97%d7%9e%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הסטרוקס, גיבורי האינדי מניו יורק מוציאים את את הסינגל החדש שלהם “Going Shopping” לקראתהאלבום “Reality Awaits” שצפוי לצאת בקיץ הקרוב  זה החומר החדש הראשון שלהם מאז האלבום המוערך מ־2020, “The New Abnormal”, שיר קליל וזורם שמשלב בין גיטרות לסינתיסייזרים, ומאמץ</v>
+        <v>השיר "חופשת מלחמה" של התקווה 6 הוא ניסיון מובהק לתרגם מציאות מלחמתית לשפה נגישה, רגשית ופופולרית – אך דווקא הפשטות הזו היא גם מקור הכוח שלו וגם נקודת החולשה המרכזית. השיר מורכב משאלות ילדים תמימות כמו "למה יש רעמים אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>הסטרוקס Going Shopping</v>
+        <v>התקווה 6 – חופשת מלחמה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>התקווה 6 – חופשת מלחמה</v>
+        <v>רביב כנר – כיסופים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%aa%d7%a7%d7%95%d7%95%d7%94-6-%d7%97%d7%95%d7%a4%d7%a9%d7%aa-%d7%9e%d7%9c%d7%97%d7%9e%d7%94/</v>
+        <v>https://yosmusic.com/%d7%a8%d7%91%d7%99%d7%91-%d7%9b%d7%a0%d7%a8-%d7%9b%d7%99%d7%a1%d7%95%d7%a4%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-11</v>
+        <v>2026-04-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "חופשת מלחמה" של התקווה 6 הוא ניסיון מובהק לתרגם מציאות מלחמתית לשפה נגישה, רגשית ופופולרית – אך דווקא הפשטות הזו היא גם מקור הכוח שלו וגם נקודת החולשה המרכזית. השיר מורכב משאלות ילדים תמימות כמו "למה יש רעמים אם</v>
+        <v>השיר "כיסופים" של רביב כנר הוא אחד הטקסטים הישירים והנוקבים ביותר שיצאו מהדור של לוחמי העשור האחרון – שיר שלא מנסה לייפות את המלחמה, אלא לשחזר את התחושה מבפנים: עייפות, בלבול, תלישות, ובעיקר געגוע. "מרוב עשן כבר אין שמיים /</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>התקווה 6 – חופשת מלחמה</v>
+        <v>רביב כנר – כיסופים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רביב כנר – כיסופים</v>
+        <v>נדב פז – שרים בכיכר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%91%d7%99%d7%91-%d7%9b%d7%a0%d7%a8-%d7%9b%d7%99%d7%a1%d7%95%d7%a4%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%a4%d7%96-%d7%a9%d7%a8%d7%99%d7%9d-%d7%91%d7%9b%d7%99%d7%9b%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-12</v>
+        <v>2026-04-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "כיסופים" של רביב כנר הוא אחד הטקסטים הישירים והנוקבים ביותר שיצאו מהדור של לוחמי העשור האחרון – שיר שלא מנסה לייפות את המלחמה, אלא לשחזר את התחושה מבפנים: עייפות, בלבול, תלישות, ובעיקר געגוע. "מרוב עשן כבר אין שמיים /</v>
+        <v>השיר "שרים בכיכר" של נדב פז פועל פחות כשיר זיכרון קלאסי ויותר כהתבוננות ביקורתית עדינה על עצם פעולת הזכירה. במקום להתמקד בדמויות הנופלים או בסיפורים אישיים, הוא מעביר את מרכז הכובד אל החברה – אל הטקס, אל הקולקטיב, ואל המתח</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רביב כנר – כיסופים</v>
+        <v>נדב פז – שרים בכיכר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C3" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%91%d7%99%d7%aa%d7%a8-%d7%91%d7%a0%d7%90%d7%99-%d7%96%d7%94-%d7%9c%d7%96%d7%94/</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>הדואט "זה לזה" של יוני רכטר ואביתר בנאי הוא מפגש נדיר בין שלושה רבדים: שירה עברית קלאסית של אברהם שלונסקי, הלחנה רגישה ועכשווית, והקשר היסטורי טעון של שכול ומלחמה. השורות הפותחות: "הדור שלמד להשמיע / ושכח להקשיב" הן לב השיר</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%99-%d7%90%d7%91%d7%99%d7%98%d7%9c-%d7%94%d7%94%d7%a6%d7%92%d7%94-%d7%97%d7%99%d7%99%d7%91%d7%aa-%d7%9c%d7%94%d7%99%d7%9e%d7%a9%d7%9a/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-13</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>השיר "ההצגה חייבת להימשך" של נוי אביטל הוא מונולוג תיאטרלי כמעט פרוע – זרם תודעה סרקסטי, חכם ומכאיב, שמצליח להפוך סיטואציה יומיומית (ארוחה משפחתית) לדרמה קיומית על זהות, כישלון ואמונה. אביטל מציג את עצמו כשחקן שמבצע הוראות, ומולו: אלוהים כבמאי</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-04-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נדב פז – שרים בכיכר</v>
+        <v>מיטל טרבלסי – יד מושטת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%93%d7%91-%d7%a4%d7%96-%d7%a9%d7%a8%d7%99%d7%9d-%d7%91%d7%9b%d7%99%d7%9b%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%98%d7%9c-%d7%98%d7%a8%d7%91%d7%9c%d7%a1%d7%99-%d7%99%d7%93-%d7%9e%d7%95%d7%a9%d7%98%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "שרים בכיכר" של נדב פז פועל פחות כשיר זיכרון קלאסי ויותר כהתבוננות ביקורתית עדינה על עצם פעולת הזכירה. במקום להתמקד בדמויות הנופלים או בסיפורים אישיים, הוא מעביר את מרכז הכובד אל החברה – אל הטקס, אל הקולקטיב, ואל המתח</v>
+        <v>"יד מושטת" בביצועה של מיטל טרבלסי, למילותיו של דוד מונסונגו, הוא שיר זיכרון שבוחר במבט מצומצם ואנושי כדי להתמודד עם אחד הנושאים הגדולים והקשים ביותר – השואה. במקום לנסות להקיף את האסון כולו, הוא מתמקד במחוות קטנות, כמעט שבריריות, שמצליחות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נדב פז – שרים בכיכר</v>
+        <v>מיטל טרבלסי – יד מושטת</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
+        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%a0%d7%99-%d7%a8%d7%9b%d7%98%d7%a8-%d7%95%d7%90%d7%91%d7%99%d7%aa%d7%a8-%d7%91%d7%a0%d7%90%d7%99-%d7%96%d7%94-%d7%9c%d7%96%d7%94/</v>
+        <v>https://yosmusic.com/%d7%aa%d7%9e%d7%a8-%d7%90%d7%99%d7%99%d7%96%d7%a0%d7%9e%d7%9f-%d7%95%d7%90%d7%99%d7%aa%d7%99-%d7%a4%d7%a8%d7%9c-%d7%98%d7%99%d7%a4%d7%94-%d7%a2%d7%9c-%d7%94%d7%9e%d7%a6%d7%95%d7%a7/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-13</v>
+        <v>2026-04-14</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>הדואט "זה לזה" של יוני רכטר ואביתר בנאי הוא מפגש נדיר בין שלושה רבדים: שירה עברית קלאסית של אברהם שלונסקי, הלחנה רגישה ועכשווית, והקשר היסטורי טעון של שכול ומלחמה. השורות הפותחות: "הדור שלמד להשמיע / ושכח להקשיב" הן לב השיר</v>
+        <v>"טיפה על המצוק" בביצוע הדואט של תמר אייזנמן ואיתי פרל הוא שיר שמתקיים כולו בתוך מרחב של שבר – אבל לא שבר מתפוצץ, אלא כזה שמחלחל לאט. הוא לא מתאר ישירות את אירועי השבעה באוקטובר, אלא את מה שנשאר אחריהם:</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,50 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יוני רכטר ואביתר בנאי – זה לזה</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%99-%d7%90%d7%91%d7%99%d7%98%d7%9c-%d7%94%d7%94%d7%a6%d7%92%d7%94-%d7%97%d7%99%d7%99%d7%91%d7%aa-%d7%9c%d7%94%d7%99%d7%9e%d7%a9%d7%9a/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-13</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>השיר "ההצגה חייבת להימשך" של נוי אביטל הוא מונולוג תיאטרלי כמעט פרוע – זרם תודעה סרקסטי, חכם ומכאיב, שמצליח להפוך סיטואציה יומיומית (ארוחה משפחתית) לדרמה קיומית על זהות, כישלון ואמונה. אביטל מציג את עצמו כשחקן שמבצע הוראות, ומולו: אלוהים כבמאי</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נוי אביטל‎ – ההצגה חייבת להימשך</v>
+        <v>תמר אייזנמן ואיתי פרל – טיפה על המצוק</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>